--- a/API-Design.xlsx
+++ b/API-Design.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Connectix\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDAB1D6-9D0E-4861-83C7-DEC0B8EDDB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE82581-4292-4A20-82AD-5C998F1F3EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0ABB4810-368D-4DBC-B04A-495B445AB6BD}"/>
   </bookViews>
@@ -37,12 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="86">
   <si>
     <t>Activity Name</t>
-  </si>
-  <si>
-    <t>Request</t>
   </si>
   <si>
     <t>Request OTP</t>
@@ -54,9 +51,6 @@
 Accept: application/json</t>
   </si>
   <si>
-    <t>Input Body</t>
-  </si>
-  <si>
     <t>{
   "phone_number": "+91-9876543210",
   "channel": "sms"
@@ -64,9 +58,6 @@
   </si>
   <si>
     <t>Field Explanation</t>
-  </si>
-  <si>
-    <t>Output Body</t>
   </si>
   <si>
     <t>{
@@ -202,9 +193,6 @@
 Secure with authentication &amp; authorization (only admins or the shopkeeper themselves should update).</t>
   </si>
   <si>
-    <t>Dealer Data API</t>
-  </si>
-  <si>
     <t>Query Parameters: Use pincode and category as filters.
 Pagination: Add page and limit parameters if dealer lists are large.
 Security: Protect with authentication (Bearer token).
@@ -231,9 +219,6 @@
 Host: api.example.com
 Authorization: Bearer &lt;your_access_token&gt;
 Accept: application/json</t>
-  </si>
-  <si>
-    <t>Dealer Product Data API</t>
   </si>
   <si>
     <t>Complete Order API</t>
@@ -279,9 +264,6 @@
 Security → Protect with authentication and validate payment.
 Scalability → Support multiple payment methods and delivery options.
 Tracking → Include order_status and estimated_delivery for customer updates.</t>
-  </si>
-  <si>
-    <t>Order Tracking API</t>
   </si>
   <si>
     <t>{
@@ -600,6 +582,580 @@
 Authorization: Bearer &lt;your_access_token&gt;
 Accept: application/json</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>GET /api/v1/dealers/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{dealer_id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/orders?page=1&amp;limit=10&amp;status=pending&amp;sort=created_at&amp;order=desc HTTP/1.1
+Host: api.example.com
+Authorization: Bearer &lt;your_access_token&gt;
+Accept: application/json</t>
+    </r>
+  </si>
+  <si>
+    <t>{dealer_id} → Path parameter identifying the dealer.
+page / limit → Pagination controls.
+status → Filter orders by status (pending, confirmed, shipped, completed, cancelled).
+sort → Field to sort by (e.g., created_at, total_amount, shopkeeper_name).
+order → Sorting order (asc or desc).</t>
+  </si>
+  <si>
+    <t>Validation → Only allow valid status transitions (e.g., pending → accepted → dispatched → delivered).
+Audit Trail → Log updates with timestamps and dealer ID for accountability.
+Bulk Updates → Consider supporting batch updates:
+http
+PUT /api/v1/dealers/{dealer_id}/orders
+with a JSON array of orders.
+Notifications → Trigger alerts to shopkeepers when status changes.</t>
+  </si>
+  <si>
+    <t>{
+  "status": "success",
+  "message": "Order updated successfully",
+  "order_id": "ord_3001",
+  "dealer_id": "dl_1001",
+  "updated_status": "accepted",
+  "remarks": "Order verified and ready for shipment",
+  "updated_at": "2026-04-21T20:15:00"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "status": "accepted",
+  "remarks": "Order verified and ready for dispatch"
+}</t>
+  </si>
+  <si>
+    <t>Dealer Dashboard  Summary API</t>
+  </si>
+  <si>
+    <t>Dealer Orders  API</t>
+  </si>
+  <si>
+    <r>
+      <t>GET /api/v1/dealers/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{dealer_id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/dashboard/summary HTTP/1.1
+Host: api.example.com
+Authorization: Bearer &lt;your_access_token&gt;
+Accept: application/json</t>
+    </r>
+  </si>
+  <si>
+    <t>Caching → Since summary data is frequently accessed, cache results for performance.
+Filters → Allow optional filters (date_range, shopkeeper_id) for more granular analytics.
+Extensibility → Add metrics like average order value, top shopkeepers, top products.
+Security → Ensure only the dealer (or authorized roles) can access their dashboard.</t>
+  </si>
+  <si>
+    <r>
+      <t>PUT /api/v1/dealers/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{dealer_id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/orders/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">{order_id} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HTTP/1.1
+Host: api.example.com
+Authorization: Bearer &lt;your_access_token&gt;
+Content-Type: application/json
+Accept: application/json</t>
+    </r>
+  </si>
+  <si>
+    <t>Release</t>
+  </si>
+  <si>
+    <t>Version 1</t>
+  </si>
+  <si>
+    <t>{
+  "status": "success",
+  "message": "Orders fetched successfully",
+  "dealer_id": "dl_10001",
+  "total_today_orders": 2,
+  "total_Pending_orders": 0,
+  "total_shopkeepers": 2,  
+  "pagination": {
+    "page": 1,
+    "limit": 10,
+    "total_records": 42,
+    "total_pages": 5
+  },
+  "orders": [
+    {
+      "order_id": "ord_3001",
+      "order_status": "Shipped",
+	  "shopkeeper_id" : "SK_1001",
+	  "shop_name": "Rajesh General Store",
+	  "shop_address": "12 Market Rd, Sector 4",
+	  "total_items": 2,
+	  "total_amount": 6700,
+      "currency": "INR",      
+      "created_at": "2026-04-19T20:10:00",
+	  "payment_type" : "Credit",
+	  "payment_status": "Pending",
+	  "delivery_date": "2026-04-21T20:10:00",
+      "items": [
+        { "product_id": "p_2001", "name": "Basmati Rice 5kg", "quantity": 10, "price": 4500 },
+        { "product_id": "p_2002", "name": "Sunflower Oil 1L", "quantity": 20, "price": 2200 }
+      ]
+    },
+	{
+      "order_id": "ord_3002",
+      "order_status": "Shipped",
+	  "shopkeeper_id" : "SK_1001",
+	  "shop_name": "Singh Brothers",
+	  "shop_address": "Shop 5, Main Bazaar",
+	  "total_items": 1,
+	  "total_amount": 2100,
+      "currency": "INR",      
+      "created_at": "2026-04-19T20:10:00",
+	  "payment_type" : "Credit",
+	  "payment_status": "Pending",
+	  "delivery_date": "",
+      "items": [
+        { "product_id": "p_2001", "name": "Basmati Rice 5kg", "quantity": 10, "price": 4500 },
+        { "product_id": "p_2002", "name": "Sunflower Oil 1L", "quantity": 20, "price": 2200 }
+      ]
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "status": "success",
+  "message": "Orders fetched successfully",
+  "dealer_id": "dl_10001",
+  "total_today_orders": 2,
+  "pagination": {
+    "page": 1,
+    "limit": 10,
+    "total_records": 42,
+    "total_pages": 5
+  },
+   "summary": {
+    "orders": {
+      "total": 120,
+      "pending": 35,
+      "confirmed": 40,
+      "shipped": 25,
+      "completed": 15,
+      "cancelled": 5
+    },
+    "revenue": {
+      "total_amount": 4500000,
+      "currency": "INR",
+      "month_to_date": 1200000,
+      "year_to_date": 3200000
+    },
+    "shopkeepers": {
+      "active": 18,
+      "new_this_month": 3
+    }
+  }  
+}</t>
+  </si>
+  <si>
+    <t>Version 2</t>
+  </si>
+  <si>
+    <t>{dealer_id} → Path parameter identifying the dealer.
+range → Time range (day, week, month, year, custom).
+metrics → Comma-separated list of analytics to fetch (revenue, orders, top_products, shopkeepers).</t>
+  </si>
+  <si>
+    <t>{
+  "status": "success",
+  "message": "Dealer insights fetched successfully",
+  "dealer_id": "dl_1001",
+  "range": "month",
+  "insights": {
+    "analytics": {
+      "revenue_trends": [
+        { "date": "2026-04-01", "amount": 150000, "currency": "INR" },
+        { "date": "2026-04-10", "amount": 220000, "currency": "INR" },
+        { "date": "2026-04-20", "amount": 180000, "currency": "INR" }
+      ],
+      "top_products": [
+        { "product_id": "p_2001", "name": "LED TV", "units_sold": 45, "revenue": 1575000 },
+        { "product_id": "p_2002", "name": "Refrigerator", "units_sold": 30, "revenue": 840000 }
+      ],
+      "shopkeeper_rankings": [
+        { "shopkeeper_id": "sh_2001", "name": "Sharma Electronics", "orders": 12, "revenue": 420000 },
+        { "shopkeeper_id": "sh_2002", "name": "Gupta Appliances", "orders": 9, "revenue": 310000 }
+      ],
+      "average_order_value": 37500,
+      "growth_rate": {
+        "month_over_month": "12%",
+        "year_over_year": "25%"
+      }
+    },
+    "performance": {
+      "fulfillment_rate": "92%",
+      "average_delivery_time": "3.5 days",
+      "cancellation_ratio": "4%",
+      "return_rate": "2%",
+      "sla_compliance": "95%",
+      "trend_analysis": {
+        "fulfillment_rate_change": "+3%",
+        "delivery_time_change": "-0.5 days",
+        "cancellation_change": "-1%"
+      }
+    }
+  },
+  "last_updated": "2026-04-21T21:20:00"
+}</t>
+  </si>
+  <si>
+    <r>
+      <t>GET /api/v1/dealers/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{dealer_id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/insights?range=month&amp;metrics=revenue,top_products,shopkeepers,performance HTTP/1.1
+Host: api.example.com
+Authorization: Bearer &lt;your_access_token&gt;
+Accept: application/json</t>
+    </r>
+  </si>
+  <si>
+    <t>Dealer Insights API</t>
+  </si>
+  <si>
+    <t>Unified Endpoint → Reduces multiple API calls for dashboard rendering.
+Modular Metrics → Allow clients to request only needed metrics via metrics query.
+Visualization-ready → Structure data for charts (line graphs for revenue, bar charts for KPIs).
+Benchmarking → Optionally include regional averages for comparison.
+Security → Ensure dealer-only access with role-based permissions.</t>
+  </si>
+  <si>
+    <t>Dealer Order Status Update API</t>
+  </si>
+  <si>
+    <t>Product Image Upload API</t>
+  </si>
+  <si>
+    <t>Request Body</t>
+  </si>
+  <si>
+    <t>Response Body</t>
+  </si>
+  <si>
+    <t>Validation Rules
+Max file size: 5 MB
+Allowed formats: .jpg, .jpeg, .png, .webp
+Auto-compress large images for mobile uploads
+Store metadata for analytics (upload source, timestamp, dealer/shopkeeper ID)</t>
+  </si>
+  <si>
+    <t>For mobile apps, use multipart upload via Retrofit or Volley (Android) or Alamofire (iOS).
+For web apps, use FormData with Axios or Fetch API.
+You can extend this endpoint to support image replacement or thumbnail generation using query params like ?replace=true or ?generate_thumbnail=true.</t>
+  </si>
+  <si>
+    <r>
+      <t>curl -X POST "https://yourdomain.com/api/products/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{product_id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/images" \
+  -H "Authorization: Bearer YOUR_TOKEN" \
+  -F "file=@/path/to/image.jpg" \
+  -F "altText=Front view of product" \
+  -F "isPrimary=true"</t>
+    </r>
+  </si>
+  <si>
+    <t>{
+  "status": "success",
+  "message": "Image uploaded successfully",
+  "data": {
+    "image_id": "img_12345",
+    "product_id": "prod_67890",
+    "image_url": "https://cdn.example.com/products/prod_67890/img_12345.webp",
+    "uploaded_at": "2026-04-23T22:56:00Z"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Shopkeeper Dealer Data API</t>
+  </si>
+  <si>
+    <t>Shopkeeper Dealer Product Data API</t>
+  </si>
+  <si>
+    <t>Shopkeeper Order Tracking API</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopkeeper Notification API
+List Notifications
+Mark Notification as Read
+</t>
+  </si>
+  <si>
+    <t>{
+  "notificationId": "abc123",
+  "status": "sent",
+  "timestamp": "2026-04-25T17:00:00Z"
+}
+[
+  {
+    "notificationId": "abc123",
+    "type": "ORDER_PLACED",
+    "title": "New Order Received",
+    "message": "Order #1234 has been placed.",
+    "status": "unread",
+    "timestamp": "2026-04-25T17:00:00Z"
+  }
+]
+{
+  "notificationId": "abc123",
+  "status": "read"
+}</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+POST  /api/shopkeepers/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{shopkeeperId}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/notifications
+Host: api.example.com
+Authorization: Bearer &lt;your_access_token&gt;
+Accept: application/json
+GET /api/shopkeepers/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{shopkeeperId}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/notifications
+Host: api.example.com
+Authorization: Bearer &lt;your_access_token&gt;
+Accept: application/json
+PATCH /api/shopkeepers/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{shopkeeperId}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/notifications/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">{notificationId}
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Host: api.example.com
+Authorization: Bearer &lt;your_access_token&gt;
+Accept: application/json
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Authentication: Use JWT or OAuth2 to ensure only authorized systems send notifications.
+Delivery Channels: Notifications can be delivered via API response, push notifications (mobile/web), or email.
+Scalability: Store notifications in a database (e.g., PostgreSQL, MongoDB) and use a message queue (Kafka, RabbitMQ) for high-volume events.</t>
+  </si>
+  <si>
+    <t>{
+  "type": "ORDER_PLACED",
+  "title": "New Order Received",
+  "message": "Order #1234 has been placed.",
+  "data": {
+    "orderId": 1234,
+    "customerName": "Rahul Sharma"
+  }
+}
+{
+  "status": "read"
+}</t>
   </si>
 </sst>
 </file>
@@ -654,7 +1210,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -662,11 +1218,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -688,6 +1272,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,65 +1645,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12D9E5C-6E53-46BD-9A09-5215F7F24154}">
   <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.54296875" customWidth="1"/>
-    <col min="4" max="4" width="37.6328125" customWidth="1"/>
-    <col min="5" max="5" width="60.6328125" customWidth="1"/>
-    <col min="6" max="6" width="45.6328125" customWidth="1"/>
-    <col min="7" max="7" width="42.6328125" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.5703125" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" customWidth="1"/>
+    <col min="5" max="5" width="60.5703125" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" customWidth="1"/>
+    <col min="7" max="7" width="42.5703125" customWidth="1"/>
     <col min="8" max="8" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -1092,30 +1713,30 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -1125,28 +1746,28 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" s="2" customFormat="1" ht="195" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -1156,25 +1777,25 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:15" s="4" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" s="4" customFormat="1" ht="195" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -1185,30 +1806,30 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1218,21 +1839,21 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15" s="2" customFormat="1" ht="267.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" s="2" customFormat="1" ht="267.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -1245,27 +1866,27 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -1276,26 +1897,26 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1305,24 +1926,24 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
     </row>
-    <row r="10" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -1334,13 +1955,26 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
     </row>
-    <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+    <row r="11" spans="1:15" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -1350,7 +1984,7 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -1366,7 +2000,7 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1382,30 +2016,30 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C14" s="7"/>
     </row>
-    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C15" s="7"/>
     </row>
-    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C16" s="7"/>
     </row>
-    <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C17" s="7"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="C18" s="7"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="C19" s="7"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C20" s="7"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C21" s="7"/>
     </row>
   </sheetData>
@@ -1416,46 +2050,395 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00F4397-58E0-4EB8-9023-F89C464B915E}">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="94.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="50.5703125" customWidth="1"/>
+    <col min="7" max="7" width="38.7109375" customWidth="1"/>
+    <col min="8" max="8" width="54.42578125" customWidth="1"/>
+    <col min="9" max="9" width="76.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="175.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" spans="1:9" ht="215.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" s="4" customFormat="1" ht="210" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="8">
+        <v>3</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" ht="180" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="8">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="C5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>